--- a/Team-Data/2012-13/2-25-2012-13.xlsx
+++ b/Team-Data/2012-13/2-25-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
         <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.582</v>
+        <v>0.574</v>
       </c>
       <c r="H2" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I2" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
         <v>81</v>
       </c>
       <c r="K2" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L2" t="n">
         <v>9.1</v>
       </c>
       <c r="M2" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O2" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="P2" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.704</v>
+        <v>0.701</v>
       </c>
       <c r="R2" t="n">
         <v>9.5</v>
@@ -712,46 +779,46 @@
         <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA2" t="n">
         <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
         <v>4</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -787,7 +854,7 @@
         <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
@@ -808,13 +875,13 @@
         <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -843,46 +910,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.526</v>
+        <v>0.518</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K3" t="n">
         <v>0.459</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N3" t="n">
         <v>0.343</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R3" t="n">
         <v>8.5</v>
@@ -915,13 +982,13 @@
         <v>19.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -936,22 +1003,22 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
         <v>19</v>
@@ -960,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1112,7 +1179,7 @@
         <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>6</v>
@@ -1145,7 +1212,7 @@
         <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1309,7 +1376,7 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>26</v>
@@ -1658,7 +1725,7 @@
         <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -1721,10 +1788,10 @@
         <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1904,7 @@
         <v>19</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
         <v>19</v>
@@ -1864,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="AO8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.621</v>
+        <v>0.614</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="J9" t="n">
         <v>85.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.474</v>
+        <v>0.472</v>
       </c>
       <c r="L9" t="n">
         <v>6.5</v>
       </c>
       <c r="M9" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O9" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P9" t="n">
         <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.5</v>
@@ -1986,13 +2053,13 @@
         <v>45.2</v>
       </c>
       <c r="U9" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="V9" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W9" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>6.6</v>
@@ -2001,19 +2068,19 @@
         <v>6.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.4</v>
+        <v>105.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2034,10 +2101,10 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>16</v>
@@ -2052,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>3</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2138,7 +2205,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L10" t="n">
         <v>6.1</v>
@@ -2147,16 +2214,16 @@
         <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="O10" t="n">
         <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.696</v>
+        <v>0.694</v>
       </c>
       <c r="R10" t="n">
         <v>12.6</v>
@@ -2165,10 +2232,10 @@
         <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2177,7 +2244,7 @@
         <v>6.9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="n">
         <v>5.6</v>
@@ -2186,13 +2253,13 @@
         <v>19.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2204,13 +2271,13 @@
         <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ10" t="n">
         <v>18</v>
@@ -2219,13 +2286,13 @@
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
         <v>20</v>
@@ -2234,10 +2301,10 @@
         <v>10</v>
       </c>
       <c r="AQ10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
@@ -2255,10 +2322,10 @@
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2601,7 +2668,7 @@
         <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,16 +3002,16 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
         <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2965,7 +3032,7 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
         <v>19</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" t="n">
         <v>28</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>0.483</v>
+        <v>0.491</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
         <v>81.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L15" t="n">
         <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.695</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
@@ -3075,7 +3142,7 @@
         <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U15" t="n">
         <v>22.1</v>
@@ -3099,13 +3166,13 @@
         <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3126,7 +3193,7 @@
         <v>21</v>
       </c>
       <c r="AK15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -3135,19 +3202,19 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3159,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>21</v>
@@ -3180,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3372,7 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>23</v>
@@ -3326,7 +3393,7 @@
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3350,13 +3417,13 @@
         <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>7.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3909,7 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
         <v>27</v>
@@ -3866,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
         <v>5</v>
@@ -3884,10 +3951,10 @@
         <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
         <v>24</v>
@@ -4051,10 +4118,10 @@
         <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
@@ -4075,7 +4142,7 @@
         <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>6</v>
@@ -4430,7 +4497,7 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4752,28 +4819,28 @@
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4818,7 +4885,7 @@
         <v>29</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
@@ -4934,7 +5001,7 @@
         <v>28</v>
       </c>
       <c r="AG25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH25" t="n">
         <v>24</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>27</v>
@@ -4979,7 +5046,7 @@
         <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
         <v>17</v>
@@ -4991,7 +5058,7 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
         <v>18</v>
@@ -5122,19 +5189,19 @@
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ26" t="n">
         <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5316,10 +5383,10 @@
         <v>17</v>
       </c>
       <c r="AM27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5516,10 +5583,10 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -5575,61 +5642,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G29" t="n">
-        <v>0.404</v>
+        <v>0.411</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O29" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P29" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0.781</v>
       </c>
       <c r="R29" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S29" t="n">
         <v>29.1</v>
       </c>
       <c r="T29" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U29" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="V29" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
@@ -5638,43 +5705,43 @@
         <v>4.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
         <v>19.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
         <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL29" t="n">
         <v>11</v>
@@ -5683,19 +5750,19 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5722,10 +5789,10 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -5757,46 +5824,46 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G30" t="n">
-        <v>0.544</v>
+        <v>0.554</v>
       </c>
       <c r="H30" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K30" t="n">
         <v>0.452</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
         <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P30" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.77</v>
+        <v>0.768</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
@@ -5823,22 +5890,22 @@
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>13</v>
@@ -5847,10 +5914,10 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
@@ -5862,10 +5929,10 @@
         <v>24</v>
       </c>
       <c r="AM30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31" t="n">
         <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.327</v>
+        <v>0.315</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J31" t="n">
         <v>82.3</v>
@@ -5966,10 +6033,10 @@
         <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N31" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="O31" t="n">
         <v>14.7</v>
@@ -5978,19 +6045,19 @@
         <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.739</v>
+        <v>0.736</v>
       </c>
       <c r="R31" t="n">
         <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U31" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V31" t="n">
         <v>15.5</v>
@@ -6005,7 +6072,7 @@
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA31" t="n">
         <v>18.8</v>
@@ -6014,19 +6081,19 @@
         <v>92</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6035,19 +6102,19 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
       </c>
       <c r="AL31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM31" t="n">
         <v>18</v>
       </c>
-      <c r="AM31" t="n">
-        <v>19</v>
-      </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6059,7 +6126,7 @@
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6068,7 +6135,7 @@
         <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV31" t="n">
         <v>28</v>
@@ -6092,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-25-2012-13</t>
+          <t>2013-02-25</t>
         </is>
       </c>
     </row>
